--- a/src/IMP/example/raw_data.xlsx
+++ b/src/IMP/example/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lizi/Desktop/biimperative/incompleteIMP/src/IMP/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9D3BE8-257F-FA41-B3DF-EEFC93438183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ACDA4D-6592-214D-8400-443875504670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3800" yWindow="500" windowWidth="21800" windowHeight="14920" activeTab="1" xr2:uid="{4A7AD6E8-1D24-084F-B0AF-95E7CADD8777}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -189,15 +189,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +517,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -530,7 +527,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -545,7 +542,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
@@ -607,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G16" si="0">AVERAGE(B3:F3)</f>
+        <f t="shared" ref="G3:G15" si="0">AVERAGE(B3:F3)</f>
         <v>0.4</v>
       </c>
       <c r="H3">
@@ -626,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M16" si="1">AVERAGE(H3:L3)</f>
+        <f t="shared" ref="M3:M15" si="1">AVERAGE(H3:L3)</f>
         <v>5</v>
       </c>
     </row>
@@ -1296,16 +1293,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -1317,140 +1314,266 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R3">
         <v>1</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <f>(P3+I3+C3)/3</f>
-        <v>9</v>
+        <f>AVERAGE(P3,I3,B3)</f>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <f>(C3+J3+Q3)/3</f>
-        <v>17</v>
+        <f>AVERAGE(Q3,J3,C3)</f>
+        <v>12.666666666666666</v>
       </c>
       <c r="Z3">
-        <f>(R3+K3+E3)/3</f>
-        <v>2</v>
+        <f t="shared" ref="Z3:AD3" si="0">AVERAGE(R3,K3,D3)</f>
+        <v>1.6666666666666667</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3" si="0">(S3+L3+F3)/3</f>
-        <v>2.3333333333333335</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3" si="1">(F3+M3+T3)/3</f>
+        <f t="shared" si="0"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="AC3">
-        <f t="shared" ref="AC3:AD3" si="2">(U3+N3+H3)/3</f>
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" si="0"/>
         <v>1.3333333333333333</v>
-      </c>
-      <c r="AD3">
-        <f t="shared" si="2"/>
-        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
       </c>
       <c r="X4">
-        <f>(P4+I4+C4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="X4:X5" si="1">AVERAGE(P4,I4,B4)</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="Y4">
-        <f>(C4+J4+Q4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="Y4:Y5" si="2">AVERAGE(Q4,J4,C4)</f>
+        <v>1.6666666666666667</v>
       </c>
       <c r="Z4">
-        <f>(R4+K4+E4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="Z4:Z5" si="3">AVERAGE(R4,K4,D4)</f>
+        <v>1</v>
       </c>
       <c r="AA4">
-        <f t="shared" ref="AA4" si="3">(S4+L4+F4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="AA4:AA5" si="4">AVERAGE(S4,L4,E4)</f>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <f t="shared" ref="AB4" si="4">(F4+M4+T4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="AB4:AB5" si="5">AVERAGE(T4,M4,F4)</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AC4">
-        <f t="shared" ref="AC4" si="5">(U4+N4+H4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="AC4:AC5" si="6">AVERAGE(U4,N4,G4)</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AD4">
-        <f t="shared" ref="AD4" si="6">(V4+O4+I4)/3</f>
-        <v>0</v>
+        <f t="shared" ref="AD4:AD5" si="7">AVERAGE(V4,O4,H4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
         <v>13</v>
       </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>8</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
       <c r="X5">
-        <f>(P5+I5+C5)/3</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <f>(C5+J5+Q5)/3</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="Z5">
-        <f>(R5+K5+E5)/3</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AA5">
-        <f t="shared" ref="AA5" si="7">(S5+L5+F5)/3</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <f t="shared" ref="AB5" si="8">(F5+M5+T5)/3</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5" si="9">(U5+N5+H5)/3</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AD5">
-        <f t="shared" ref="AD5" si="10">(V5+O5+I5)/3</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>2.6666666666666665</v>
       </c>
     </row>
   </sheetData>
